--- a/Samples/09_ISOS_V1_degrading.xlsx
+++ b/Samples/09_ISOS_V1_degrading.xlsx
@@ -35,6 +35,9 @@
     <sheet name="JV_Dark_#012_t0600h" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="JV_#012_t0600h" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="Stress_161940" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Stress_161526" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Stress_161542" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Stress_161740" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35594,6 +35597,212 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>elapsed_h</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>t_s</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>j</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pce</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0.000147</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.528</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.000704</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.533</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0.00126</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4.537</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0.001817</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0.002373</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8.544</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -36868,6 +37077,418 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>elapsed_h</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>t_s</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>j</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pce</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0.000122</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.000679</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.444</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0.001235</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4.448</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0.001793</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6.453</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0.002349</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8.458</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0.002907</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10.464</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0.003464</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12.469</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0.004021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14.475</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>elapsed_h</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>t_s</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>j</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pce</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3.7e-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.132</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.000692</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.492</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.989005485714284</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>stress_dark</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
